--- a/dashboard_cyber.xlsx
+++ b/dashboard_cyber.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PauloCaceres\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{473D0567-2989-4364-A4D1-5F1699A9BBEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD95F19-2FDB-4052-BBA4-00CD97CADAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22350" yWindow="1665" windowWidth="13830" windowHeight="7965" activeTab="2" xr2:uid="{C55A9B46-5ADC-4F1B-B68A-DDFA542FF3C4}"/>
+    <workbookView xWindow="-21885" yWindow="3150" windowWidth="13830" windowHeight="7965" xr2:uid="{C55A9B46-5ADC-4F1B-B68A-DDFA542FF3C4}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3041" uniqueCount="2910">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3041" uniqueCount="2928">
   <si>
     <t>Año,Mes,Día,HoraCerrada,count order,bruto,total neto,ticket promedio,Cantidad</t>
   </si>
@@ -8753,6 +8753,60 @@
   </si>
   <si>
     <t>9866,Catit pixi bebedero de agua inteligente,1</t>
+  </si>
+  <si>
+    <t>2026,junio,1,0,440,$28538891,$23982229,$54505,1928</t>
+  </si>
+  <si>
+    <t>2026,junio,1,1,180,$11940259,$10033812,$55743,899</t>
+  </si>
+  <si>
+    <t>2026,junio,1,2,77,$4880319,$4101099,$53261,269</t>
+  </si>
+  <si>
+    <t>2026,junio,1,3,19,$1117089,$938733,$49407,61</t>
+  </si>
+  <si>
+    <t>2026,junio,1,4,20,$1313509,$1103791,$55190,90</t>
+  </si>
+  <si>
+    <t>2026,junio,1,5,25,$1686657,$1417355,$56694,92</t>
+  </si>
+  <si>
+    <t>2026,junio,1,6,46,$3390082,$2848804,$61931,146</t>
+  </si>
+  <si>
+    <t>2026,junio,1,7,131,$8636885,$7257884,$55404,411</t>
+  </si>
+  <si>
+    <t>2026,junio,1,8,241,$15368304,$12914533,$53587,871</t>
+  </si>
+  <si>
+    <t>2026,junio,1,9,372,$25289715,$21251846,$57129,1589</t>
+  </si>
+  <si>
+    <t>2026,junio,1,10,420,$25703476,$21599527,$51427,1685</t>
+  </si>
+  <si>
+    <t>2026,junio,1,11,509,$31495329,$26466602,$51997,2049</t>
+  </si>
+  <si>
+    <t>2026,junio,1,12,441,$27652227,$23237128,$52692,1672</t>
+  </si>
+  <si>
+    <t>2026,junio,1,13,410,$27056222,$22736284,$55454,1343</t>
+  </si>
+  <si>
+    <t>2026,junio,1,14,470,$31030590,$26076108,$55481,1918</t>
+  </si>
+  <si>
+    <t>2026,junio,1,15,405,$24203302,$20338892,$50219,1253</t>
+  </si>
+  <si>
+    <t>2026,junio,1,16,375,$23546580,$19787039,$52765,1185</t>
+  </si>
+  <si>
+    <t>2026,junio,1,17,371,$21419006,$17999140,$48515,1207</t>
   </si>
 </sst>
 </file>
@@ -9623,92 +9677,92 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>2911</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2912</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>2913</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>2914</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>2917</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>2918</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>2920</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>2921</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>2926</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>2927</v>
       </c>
     </row>
   </sheetData>
